--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_902_Sardinia_Italy.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_902_Sardinia_Italy.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc0529b87877a4335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R117c24be41c04fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R86ed457cdaea497b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf56d085d9f2741a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6b076e72add94227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re9b10a7dbe014206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R49c9a2c510f54626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R5b2eaf5fcc6f4511"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4fe1a0e218724b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R65291ce42b524cb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb8800ae277184b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9b1f544989a641a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ902CommercialTable" displayName="EEZ902CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ902CommercialTable" displayName="EEZ902CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ902FunctionalTable" displayName="EEZ902FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ902FunctionalTable" displayName="EEZ902FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ902ValidationTable" displayName="EEZ902ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ902ValidationTable" displayName="EEZ902ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10409,7 +10363,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe5f9af70f5a4a14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6f8ed8452674ffb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10419,20 +10373,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10440,714 +10384,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>87.425796213</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1100000000000003</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931348</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>87.425796213</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$146,A2,'Species'!$U$2:$U$146))</x:f>
-        <x:v>11262.624277781251</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1100000000000003</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931348</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11262.62427778126</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>-9.094947017729282e-12</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>0.9999999999999992</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>-8.07533554650461e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1020.4122986929999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.255259330169545</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1799.9453952973154</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1020.4122986929999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2056.2198356383315</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$146,A3,'Species'!$U$2:$U$146))</x:f>
-        <x:v>2098192.0091018523</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.255259330169545</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1799.9453952973154</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1836686.418337214</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>261505.59076463827</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1423790082802399</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.14237900828023986</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>274.463429871</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.263074407746987</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>183.26283800053247</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>274.463429871</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>199.33155736685742</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$146,A4,'Species'!$U$2:$U$146))</x:f>
-        <x:v>54709.22291643569</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.263074407746987</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>183.26283800053247</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>50298.94708551958</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4410.275830916107</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0876812753837102</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08768127538371014</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>164.13643932899998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6246565330567333</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>421.3631315889615</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>164.13643932899998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>664.3114343324733</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$146,A5,'Species'!$U$2:$U$146))</x:f>
-        <x:v>109037.71343687296</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6246565330567333</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>421.3631315889615</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>69161.04408352902</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>39876.66935334394</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.576577029478951</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.576577029478951</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>273.154652199</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1035280567689836</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>126.91941356698706</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>273.154652199</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>132.44917979544712</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$146,A6,'Species'!$U$2:$U$146))</x:f>
-        <x:v>36179.10964106818</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1035280567689836</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>126.91941356698706</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>34668.628270191395</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1510.4813708767833</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0435691126601487</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04356911266014865</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.08000155</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.08000155</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$146,A7,'Species'!$U$2:$U$146))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1.0071598427792168</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>1.0071598427792168</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3731.9795286048993</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7048754573617266</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>506.84533938268754</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3731.9795286048993</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>740.7882368789798</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$146,A8,'Species'!$U$2:$U$146))</x:f>
-        <x:v>2764606.5350636696</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7048754573617266</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>506.84533938268754</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1891536.4307449926</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>873070.104318677</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4615666344712237</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.46156663447122365</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8261.5028916578</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.373806723106001</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>236.48670111355702</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8261.5028916578</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>500.1174537175089</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$146,A9,'Species'!$U$2:$U$146))</x:f>
-        <x:v>4131721.7900557355</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.373806723106001</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>236.48670111355702</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1953735.565088265</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2177986.2249674704</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.1147804564171273</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.1147804564171273</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3.1468443</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3.1468443</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$146,A10,'Species'!$U$2:$U$146))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>704.4906854193291</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>704.4906854193291</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>369.45178555920006</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.940061033797329</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>871.0859998713087</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>369.45178555920006</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>940.3785469312301</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$146,A11,'Species'!$U$2:$U$146))</x:f>
-        <x:v>347424.53326530894</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.940061033797329</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>871.0859998713087</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>321824.2780280761</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>25600.255237232835</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.079547308842248</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.07954730884224794</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>296.6206308735001</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.1071130404460146</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1279.7143515766597</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>296.6206308735001</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1661.1455493858118</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$146,A12,'Species'!$U$2:$U$146))</x:f>
-        <x:v>492730.0408315264</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.1071130404460146</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1279.7143515766597</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>379589.6783025409</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>113140.36252898548</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.298059639121194</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.29805963912119404</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1254.7170030507998</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.426833073878229</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2671.979205065735</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1254.7170030507998</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2728.454238179031</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$146,A13,'Species'!$U$2:$U$146))</x:f>
-        <x:v>3423437.924689247</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.426833073878229</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2671.979205065735</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>3352577.740394138</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>70860.18429510901</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0211360301780141</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.021136030178014156</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428ba9b930524290"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23010454dc04581"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11157,20 +10637,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11178,1416 +10648,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2035.232018737</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7037448175779923</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>505.5275372329032</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2035.232018737</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>542.7756753052944</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$146,A2,'Species'!$U$2:$U$146))</x:f>
-        <x:v>1104674.4333729327</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7037448175779923</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>505.5275372329032</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1028865.8301296656</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>75808.60324326716</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0736817192516863</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07368171925168628</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>139.141145245</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8199999999999994</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>660.6934480075951</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>139.141145245</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$146,A3,'Species'!$U$2:$U$146))</x:f>
-        <x:v>91929.64301164473</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8199999999999994</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>660.6934480075951</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>91929.64301164463</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1.0186340659856796e-10</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.1080583287554487e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>520.585688106</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.84995457023927</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>707.8717329585824</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>520.585688106</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1459.0367409979713</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$146,A4,'Species'!$U$2:$U$146))</x:f>
-        <x:v>759553.6457843645</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.84995457023927</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>707.8717329585824</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>368507.89319303026</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>391045.7525913343</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.061159773819277</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.061159773819277</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>825.5666043221</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.340216042282928</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2188.850209266474</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>825.5666043221</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2367.512616788946</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$146,A5,'Species'!$U$2:$U$146))</x:f>
-        <x:v>1954539.3517321795</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.340216042282928</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2188.850209266474</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1807041.634633841</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>147497.71709833853</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0816238620468897</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08162386204688961</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>22.005652001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>22.005652001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$146,A6,'Species'!$U$2:$U$146))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>50412.036347155365</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>50412.036347155365</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1189.7665550786</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.415527367720635</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2603.3188782638745</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1189.7665550786</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2652.1335940754752</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$146,A7,'Species'!$U$2:$U$146))</x:f>
-        <x:v>3155419.8498314046</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.415527367720635</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2603.3188782638745</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3097341.7335630953</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>58078.1162683093</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0187509552591403</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.018750955259140185</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>72.52445660329998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8200805360069086</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>660.8159790279926</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>72.52445660329998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>667.1995704201089</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$146,A8,'Species'!$U$2:$U$146))</x:f>
-        <x:v>48388.286290673575</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8200805360069086</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>660.8159790279926</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>47925.319793782844</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>462.9664968907309</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0096601650001047</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.009660165000104802</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>146.88517904900002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.160459012873139</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1446.9682870691151</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>146.88517904900002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1796.6753051179555</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$146,A9,'Species'!$U$2:$U$146))</x:f>
-        <x:v>263904.9738851676</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.160459012873139</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1446.9682870691151</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>212538.19592437183</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>51366.77796079579</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2416825725719145</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.24168257257191458</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>151.7971404152</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.405605423622966</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2544.5173917806133</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>151.7971404152</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2638.1207681184774</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$146,A10,'Species'!$U$2:$U$146))</x:f>
-        <x:v>400459.1886703358</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.405605423622966</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2544.5173917806133</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>386250.46380904026</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>14208.724861295545</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0367862985099747</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.036786298509974724</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>161.026699327</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.277068881191613</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>189.26437772382633</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>161.026699327</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>207.52052034121857</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$146,A11,'Species'!$U$2:$U$146))</x:f>
-        <x:v>33416.344433167986</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.277068881191613</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>189.26437772382633</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>30476.618045046336</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2939.7263881216495</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0964584188369113</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.09645841883691134</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>61.514243709000006</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.162447611458774</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1453.6090275201807</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>61.514243709000006</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2078.6367979810852</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$146,A12,'Species'!$U$2:$U$146))</x:f>
-        <x:v>127865.77057350388</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.162447611458774</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1453.6090275201807</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>89417.65997647888</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>38448.11059702499</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.4299834127524549</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.42998341275245494</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3.6608044034000002</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3.6608044034000002</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$146,A13,'Species'!$U$2:$U$146))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4401.254936298637</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>4401.254936298637</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2059.4280533851</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4414982236327787</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>276.3746614769459</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2059.4280533851</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>553.3740983254504</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$146,A14,'Species'!$U$2:$U$146))</x:f>
-        <x:v>1139634.1421081172</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4414982236327787</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>276.3746614769459</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>569173.7310904327</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>570460.4110176845</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.0022606101739564</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.0022606101739564</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>3645.4973046072996</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.1780835879490206</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>150.68970682932442</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>3645.4973046072996</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>235.80054192916984</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$146,A15,'Species'!$U$2:$U$146))</x:f>
-        <x:v>859610.2400277292</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.1780835879490206</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>150.68970682932442</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>549338.9200783664</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>310271.3199493628</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5648085518956143</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5648085518956144</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2453.4982928081</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.886731491661761</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>770.4269950523719</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2453.4982928081</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1156.9476883425762</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$146,A16,'Species'!$U$2:$U$146))</x:f>
-        <x:v>2838569.178216788</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.886731491661761</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>770.4269950523719</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1890241.317094269</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>948327.861122519</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.5016967159411767</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5016967159411766</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>317.688622315</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.8363674089579582</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>68.60683882755045</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>317.688622315</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>138.19881313325013</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$146,A17,'Species'!$U$2:$U$146))</x:f>
-        <x:v>43904.190549870356</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.8363674089579582</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>68.60683882755045</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>21795.61210851175</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>22108.578441358608</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.014359144000578</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.014359144000578</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>2.313730428</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.2930846265380054</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>19.63742894113659</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>2.313730428</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>19.698020915723713</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$146,A18,'Species'!$U$2:$U$146))</x:f>
-        <x:v>45.575910364090376</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.2930846265380054</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>19.63742894113659</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>45.43571686879555</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0.14019349529482383</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0030855350142194</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0030855350142193145</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>113.436730544</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2432088504728966</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>175.0688385240597</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>113.436730544</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>187.70708906326067</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$146,A19,'Species'!$U$2:$U$146))</x:f>
-        <x:v>21292.87848326771</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2432088504728966</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>175.0688385240597</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>19859.236662304804</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1433.6418209629046</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0721901775652902</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.07219017756529018</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>389.395715329</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3863010133357196</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>243.38903754738223</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>389.395715329</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>244.64861597467007</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$146,A20,'Species'!$U$2:$U$146))</x:f>
-        <x:v>95265.12282170646</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3863010133357196</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>243.38903754738223</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>94774.64837899974</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>490.47444270671986</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0051751649950242</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.005175164995024129</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>437.097272025</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.4320440849220377</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>270.4232854918635</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>437.097272025</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>555.4044135118614</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$146,A21,'Species'!$U$2:$U$146))</x:f>
-        <x:v>242765.75401667968</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.4320440849220377</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>270.4232854918635</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>118201.2803805313</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>124564.47363614838</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>2.053833539155682</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>1.0538335391556821</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>385.4685549981</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.1112247125850025</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>129.18875489689407</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>385.4685549981</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>133.30849513589604</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$146,A22,'Species'!$U$2:$U$146))</x:f>
-        <x:v>51386.23298900508</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.1112247125850025</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>129.18875489689407</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>49798.20267210947</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1588.0303168956088</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0318893098883872</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.03188930988838717</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>389.131017282</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.2268247936407892</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>168.58727606602108</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>389.131017282</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>205.74218095327802</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$146,A23,'Species'!$U$2:$U$146))</x:f>
-        <x:v>80060.6641721664</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.2268247936407892</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>168.58727606602108</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>65602.53823637216</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>14458.125935794247</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.2203897337584753</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.22038973375847518</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>142.13078732799997</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.5108056725994614</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>324.194522308232</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>142.13078732799997</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>412.476974143717</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$146,A24,'Species'!$U$2:$U$146))</x:f>
-        <x:v>58625.67708971758</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.5108056725994614</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>324.194522308232</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>46078.02270309387</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>12547.654386623712</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.2723132124717065</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.27231321247170637</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>15.206221939999999</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.5722764047346267</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>373.4877867606675</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>15.206221939999999</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>400.36317083384085</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$146,A25,'Species'!$U$2:$U$146))</x:f>
-        <x:v>6088.011232301518</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.5722764047346267</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>373.4877867606675</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>5679.338177362103</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>408.6730549394151</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0719578658950772</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.07195786589507733</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>57.092811915</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.820552111722872</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>661.5339112847821</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>57.092811915</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>661.9844665294137</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$146,A26,'Species'!$U$2:$U$146))</x:f>
-        <x:v>37794.55463821543</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.820552111722872</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>661.5339112847821</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>37768.83117237636</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>25.723465839066193</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0006810765660623</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0006810765660622298</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R577f54190df7489b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ef33da7d896420c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12762,7 +11313,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12861,7 +11412,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>13470007.00112476</x:v>
+        <x:v>9902046.85245751</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12875,7 +11426,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>13470007.001124758</x:v>
+        <x:v>10683465.39783505</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12889,7 +11440,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-3567960.148667248</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12903,7 +11454,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-2786541.6032897085</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12914,9 +11465,9 @@
         <x:v>EEZ_902</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12928,47 +11479,19 @@
         <x:v>EEZ_902</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_902</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_902</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57325a780a7b4889"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d646f35270c4486"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13015,7 +11538,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
